--- a/Pacote MoT 20 bytes.xlsx
+++ b/Pacote MoT 20 bytes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.0GitHub\Framework\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\.0GitHub\Framework_basic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41B9211B-10D5-475B-BAAB-6656FFF68271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70070FED-896A-4950-B509-8B8B86D36BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="16608" windowHeight="8712" xr2:uid="{FB505E60-EE52-4C8B-938D-5B253E8A8EE2}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB505E60-EE52-4C8B-938D-5B253E8A8EE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
